--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Standard capability or configuration</t>
+          <t>Standard capability or configuration of brokerverse-platform</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$K$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$J$205</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fit-Gap'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -711,13 +711,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -746,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -818,6 +822,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -885,6 +890,7 @@
         <v>201</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -940,6 +946,8 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -974,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -997,6 +1005,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1311,26 +1320,8 @@
       </c>
       <c r="D20" s="14" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Fit-Gap</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>In the BIBS environment</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Available / Partly available / Planned for</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D21"/>
+  <autoFilter ref="A4:D20"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1710,7 +1701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1723,7 +1714,6 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1751,7 +1741,6 @@
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n"/>
-      <c r="K3" s="24" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
@@ -1804,11 +1793,6 @@
           <t>Impact</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>In the BIBS environment</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -1861,11 +1845,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -1918,11 +1897,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -1975,11 +1949,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -2032,11 +2001,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2066,7 +2030,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2087,11 +2051,6 @@
       <c r="J9" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2082,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -2144,11 +2103,6 @@
       <c r="J10" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2134,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -2201,11 +2155,6 @@
       <c r="J11" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2186,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -2258,11 +2207,6 @@
       <c r="J12" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2238,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -2315,11 +2259,6 @@
       <c r="J13" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2290,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -2372,11 +2311,6 @@
       <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2342,7 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -2429,11 +2363,6 @@
       <c r="J15" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2394,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -2486,11 +2415,6 @@
       <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2446,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -2543,11 +2467,6 @@
       <c r="J17" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2498,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -2600,11 +2519,6 @@
       <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2550,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -2657,11 +2571,6 @@
       <c r="J19" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2602,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -2714,11 +2623,6 @@
       <c r="J20" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2654,7 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -2771,11 +2675,6 @@
       <c r="J21" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2706,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2828,11 +2727,6 @@
       <c r="J22" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2758,7 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -2885,11 +2779,6 @@
       <c r="J23" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2810,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -2942,11 +2831,6 @@
       <c r="J24" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2862,7 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -2999,11 +2883,6 @@
       <c r="J25" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3035,7 +2914,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -3056,11 +2935,6 @@
       <c r="J26" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3092,7 +2966,7 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -3113,11 +2987,6 @@
       <c r="J27" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3018,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -3170,11 +3039,6 @@
       <c r="J28" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3070,7 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -3227,11 +3091,6 @@
       <c r="J29" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3122,7 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -3284,11 +3143,6 @@
       <c r="J30" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3174,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -3341,11 +3195,6 @@
       <c r="J31" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3226,7 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -3398,11 +3247,6 @@
       <c r="J32" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K32" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3278,7 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -3455,11 +3299,6 @@
       <c r="J33" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3330,7 @@
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -3512,11 +3351,6 @@
       <c r="J34" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3382,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -3569,11 +3403,6 @@
       <c r="J35" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3434,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -3626,11 +3455,6 @@
       <c r="J36" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3486,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -3683,11 +3507,6 @@
       <c r="J37" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3538,7 @@
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -3740,11 +3559,6 @@
       <c r="J38" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3590,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -3797,11 +3611,6 @@
       <c r="J39" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3642,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -3854,11 +3663,6 @@
       <c r="J40" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3694,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -3911,11 +3715,6 @@
       <c r="J41" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3746,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -3968,11 +3767,6 @@
       <c r="J42" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4004,7 +3798,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -4025,11 +3819,6 @@
       <c r="J43" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4061,7 +3850,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -4082,11 +3871,6 @@
       <c r="J44" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4118,7 +3902,7 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -4139,11 +3923,6 @@
       <c r="J45" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4175,7 +3954,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -4196,11 +3975,6 @@
       <c r="J46" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4006,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of BIBS, available in the BIBS environment.</t>
+          <t>The base product creates and changes users directly by an administrator; the request with a chosen approver, draft, edit, cancel and submit is an extension of the platform.</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4253,11 +4027,6 @@
       <c r="J47" s="12" t="inlineStr">
         <is>
           <t>Scope of FRUM.009; UIDM-ISC interface (Annex N).</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4058,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -4310,11 +4079,6 @@
       <c r="J48" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4110,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -4367,11 +4131,6 @@
       <c r="J49" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>Partly available</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4162,7 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -4424,11 +4183,6 @@
       <c r="J50" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4214,7 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -4481,11 +4235,6 @@
       <c r="J51" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4266,7 @@
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -4538,11 +4287,6 @@
       <c r="J52" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4318,7 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -4595,11 +4339,6 @@
       <c r="J53" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4370,7 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -4652,11 +4391,6 @@
       <c r="J54" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4422,7 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -4709,11 +4443,6 @@
       <c r="J55" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4474,7 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -4766,11 +4495,6 @@
       <c r="J56" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4526,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4823,11 +4547,6 @@
       <c r="J57" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4578,7 @@
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -4880,11 +4599,6 @@
       <c r="J58" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4630,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -4937,11 +4651,6 @@
       <c r="J59" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4682,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -4994,11 +4703,6 @@
       <c r="J60" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5030,7 +4734,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5051,11 +4755,6 @@
       <c r="J61" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5087,7 +4786,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -5108,11 +4807,6 @@
       <c r="J62" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5144,7 +4838,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
+          <t>Extension of the platform: returned requests corrected and re-submitted, cancellation with a reason, own requests with status and history, notices in the system.</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5165,11 +4859,6 @@
       <c r="J63" s="12" t="inlineStr">
         <is>
           <t>Annex T.</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>Partly available</t>
         </is>
       </c>
     </row>
@@ -5201,7 +4890,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -5222,11 +4911,6 @@
       <c r="J64" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5258,7 +4942,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5279,11 +4963,6 @@
       <c r="J65" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5315,7 +4994,7 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -5336,11 +5015,6 @@
       <c r="J66" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5046,7 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -5393,11 +5067,6 @@
       <c r="J67" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5098,7 @@
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -5450,11 +5119,6 @@
       <c r="J68" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5150,7 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5507,11 +5171,6 @@
       <c r="J69" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K69" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5202,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
+          <t>Extension of the platform: upload of a template file checked row by row, draft batch decided by an approver as a whole.</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -5564,11 +5223,6 @@
       <c r="J70" s="12" t="inlineStr">
         <is>
           <t>FRUM.011; go-live load.</t>
-        </is>
-      </c>
-      <c r="K70" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5623,11 +5277,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -5680,11 +5329,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -5737,11 +5381,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -5794,11 +5433,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -5828,7 +5462,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -5849,11 +5483,6 @@
       <c r="J75" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K75" s="12" t="inlineStr">
-        <is>
-          <t>Partly available</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5514,7 @@
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -5906,11 +5535,6 @@
       <c r="J76" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5566,7 @@
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -5963,11 +5587,6 @@
       <c r="J77" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5618,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -6020,11 +5639,6 @@
       <c r="J78" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6056,7 +5670,7 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6077,11 +5691,6 @@
       <c r="J79" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6113,7 +5722,7 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -6134,11 +5743,6 @@
       <c r="J80" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K80" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6170,7 +5774,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6191,11 +5795,6 @@
       <c r="J81" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6227,7 +5826,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -6248,11 +5847,6 @@
       <c r="J82" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6284,7 +5878,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6305,11 +5899,6 @@
       <c r="J83" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K83" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6341,7 +5930,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -6362,11 +5951,6 @@
       <c r="J84" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K84" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6398,7 +5982,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6419,11 +6003,6 @@
       <c r="J85" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6034,7 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
+          <t>Extension of the platform: requests assigned to the approver, approve, reject or return with remarks, automatic application on approval, second approval of privileged or out-of-hours changes.</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -6476,11 +6055,6 @@
       <c r="J86" s="12" t="inlineStr">
         <is>
           <t>FRUM.010; Annex S.</t>
-        </is>
-      </c>
-      <c r="K86" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6535,11 +6109,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -6592,11 +6161,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -6649,11 +6213,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K89" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -6706,11 +6265,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K90" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -6740,7 +6294,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -6761,11 +6315,6 @@
       <c r="J91" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K91" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6346,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -6818,11 +6367,6 @@
       <c r="J92" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K92" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6398,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -6875,11 +6419,6 @@
       <c r="J93" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K93" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6450,7 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -6932,11 +6471,6 @@
       <c r="J94" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K94" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6502,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -6989,11 +6523,6 @@
       <c r="J95" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K95" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7025,7 +6554,7 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -7046,11 +6575,6 @@
       <c r="J96" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K96" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7082,7 +6606,7 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -7103,11 +6627,6 @@
       <c r="J97" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K97" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7139,7 +6658,7 @@
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
@@ -7160,11 +6679,6 @@
       <c r="J98" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K98" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7196,7 +6710,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7217,11 +6731,6 @@
       <c r="J99" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K99" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7253,7 +6762,7 @@
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -7274,11 +6783,6 @@
       <c r="J100" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K100" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7310,7 +6814,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7331,11 +6835,6 @@
       <c r="J101" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K101" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7367,7 +6866,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -7388,11 +6887,6 @@
       <c r="J102" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K102" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7424,7 +6918,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -7445,11 +6939,6 @@
       <c r="J103" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K103" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7481,7 +6970,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -7502,11 +6991,6 @@
       <c r="J104" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K104" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7022,7 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -7559,11 +7043,6 @@
       <c r="J105" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K105" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7074,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -7616,11 +7095,6 @@
       <c r="J106" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K106" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7126,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -7673,11 +7147,6 @@
       <c r="J107" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K107" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7178,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -7730,11 +7199,6 @@
       <c r="J108" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K108" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7230,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -7787,11 +7251,6 @@
       <c r="J109" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K109" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7282,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -7844,11 +7303,6 @@
       <c r="J110" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K110" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7334,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -7901,11 +7355,6 @@
       <c r="J111" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K111" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7386,7 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -7958,11 +7407,6 @@
       <c r="J112" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K112" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7438,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8015,11 +7459,6 @@
       <c r="J113" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K113" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8051,7 +7490,7 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -8072,11 +7511,6 @@
       <c r="J114" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K114" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8108,7 +7542,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -8129,11 +7563,6 @@
       <c r="J115" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K115" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8165,7 +7594,7 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -8186,11 +7615,6 @@
       <c r="J116" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K116" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8222,7 +7646,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -8243,11 +7667,6 @@
       <c r="J117" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K117" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8279,7 +7698,7 @@
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -8300,11 +7719,6 @@
       <c r="J118" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K118" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8336,7 +7750,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -8357,11 +7771,6 @@
       <c r="J119" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K119" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8393,7 +7802,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -8414,11 +7823,6 @@
       <c r="J120" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K120" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8450,7 +7854,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -8471,11 +7875,6 @@
       <c r="J121" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K121" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8507,7 +7906,7 @@
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -8528,11 +7927,6 @@
       <c r="J122" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K122" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8564,7 +7958,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -8585,11 +7979,6 @@
       <c r="J123" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K123" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8010,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
@@ -8642,11 +8031,6 @@
       <c r="J124" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K124" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8062,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>Extension of BIBS: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
+          <t>Extension of the platform: group-profile requests approved by approvers in order and implemented by the System Administrator, with the privilege level of the profile.</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -8699,11 +8083,6 @@
       <c r="J125" s="12" t="inlineStr">
         <is>
           <t>FRUM.005, FRUM.006.</t>
-        </is>
-      </c>
-      <c r="K125" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
         </is>
       </c>
     </row>
@@ -8758,11 +8137,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K126" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
@@ -8815,11 +8189,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K127" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -8872,11 +8241,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K128" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -8929,11 +8293,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K129" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -8986,11 +8345,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K130" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
@@ -9043,11 +8397,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K131" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -9100,11 +8449,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K132" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -9157,11 +8501,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K133" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -9214,11 +8553,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K134" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
@@ -9271,11 +8605,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K135" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -9328,11 +8657,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K136" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -9385,11 +8709,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K137" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -9442,11 +8761,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K138" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -9499,11 +8813,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K139" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -9556,11 +8865,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K140" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
@@ -9613,11 +8917,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K141" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -9670,11 +8969,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K142" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
@@ -9727,11 +9021,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K143" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -9784,11 +9073,6 @@
           <t>FRUM.007; Annex V.</t>
         </is>
       </c>
-      <c r="K144" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
@@ -9841,11 +9125,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K145" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -9898,11 +9177,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K146" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
@@ -9955,11 +9229,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K147" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -10012,11 +9281,6 @@
           <t>BDOI IT registration; no change to the screens.</t>
         </is>
       </c>
-      <c r="K148" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
@@ -10069,11 +9333,6 @@
           <t>Annex C; Annex Y.</t>
         </is>
       </c>
-      <c r="K149" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -10126,11 +9385,6 @@
           <t>Annex C; Annex Y.</t>
         </is>
       </c>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
@@ -10183,11 +9437,6 @@
           <t>Annex C; Annex Y.</t>
         </is>
       </c>
-      <c r="K151" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -10240,11 +9489,6 @@
           <t>Annex C; Annex Y.</t>
         </is>
       </c>
-      <c r="K152" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
@@ -10297,11 +9541,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K153" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -10354,11 +9593,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K154" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
@@ -10411,11 +9645,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K155" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -10468,11 +9697,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K156" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
@@ -10525,11 +9749,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K157" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -10582,11 +9801,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K158" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
@@ -10639,11 +9853,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K159" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -10696,11 +9905,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K160" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
@@ -10753,11 +9957,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K161" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -10810,11 +10009,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K162" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
@@ -10867,11 +10061,6 @@
           <t>FRUM.005.06.</t>
         </is>
       </c>
-      <c r="K163" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -10924,11 +10113,6 @@
           <t>FRUM.008.</t>
         </is>
       </c>
-      <c r="K164" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="12" t="inlineStr">
@@ -10954,7 +10138,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>Within the the system sizing (145 concurrent users); online p95 under 3 seconds, reports under 20 seconds</t>
+          <t>Within the system sizing (145 concurrent users); online p95 under 3 seconds, reports under 20 seconds</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -10975,11 +10159,6 @@
       <c r="J165" s="12" t="inlineStr">
         <is>
           <t>Annex X</t>
-        </is>
-      </c>
-      <c r="K165" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -11030,11 +10209,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K166" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="12" t="inlineStr">
@@ -11083,11 +10257,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K167" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -11136,11 +10305,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K168" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -11189,11 +10353,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K169" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -11246,11 +10405,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K170" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="12" t="inlineStr">
@@ -11299,11 +10453,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K171" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -11352,11 +10501,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K172" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
@@ -11409,11 +10553,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K173" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -11466,11 +10605,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K174" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="12" t="inlineStr">
@@ -11523,11 +10657,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K175" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -11576,11 +10705,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K176" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="12" t="inlineStr">
@@ -11633,11 +10757,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K177" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -11690,11 +10809,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K178" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="12" t="inlineStr">
@@ -11747,11 +10861,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K179" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -11804,11 +10913,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K180" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="12" t="inlineStr">
@@ -11861,11 +10965,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K181" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -11918,11 +11017,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K182" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="12" t="inlineStr">
@@ -11975,11 +11069,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K183" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -12028,11 +11117,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K184" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="12" t="inlineStr">
@@ -12081,11 +11165,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K185" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -12138,11 +11217,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K186" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
@@ -12191,11 +11265,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K187" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -12248,11 +11317,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K188" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="12" t="inlineStr">
@@ -12305,11 +11369,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K189" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
@@ -12358,11 +11417,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K190" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="12" t="inlineStr">
@@ -12388,7 +11442,7 @@
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>Retention rules and the monthly retention review; physical archive and purge follow the the system retention decision (Q39, UQ12)</t>
+          <t>Retention rules and the monthly retention review; physical archive and purge follow the system retention decision (Q39, UQ12)</t>
         </is>
       </c>
       <c r="G191" s="12" t="inlineStr">
@@ -12409,11 +11463,6 @@
       <c r="J191" s="12" t="inlineStr">
         <is>
           <t>Annex X</t>
-        </is>
-      </c>
-      <c r="K191" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -12464,11 +11513,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K192" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="12" t="inlineStr">
@@ -12517,11 +11561,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K193" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
@@ -12570,11 +11609,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K194" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
@@ -12627,11 +11661,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K195" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
@@ -12684,11 +11713,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K196" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" s="12" t="inlineStr">
@@ -12741,11 +11765,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K197" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
@@ -12798,11 +11817,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K198" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
@@ -12855,11 +11869,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K199" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
@@ -12912,11 +11921,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K200" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
@@ -12969,11 +11973,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K201" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
@@ -13026,11 +12025,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K202" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" s="12" t="inlineStr">
@@ -13083,11 +12077,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K203" s="12" t="inlineStr">
-        <is>
-          <t>Partly available</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
@@ -13140,11 +12129,6 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K204" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
@@ -13197,16 +12181,11 @@
           <t>Annex X</t>
         </is>
       </c>
-      <c r="K205" s="12" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K205"/>
+  <autoFilter ref="A4:J205"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H705">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
@@ -13216,7 +12195,7 @@
       <formula>"Configure"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:K705">
+  <conditionalFormatting sqref="A5:J705">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
@@ -965,7 +965,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1326,7 +1326,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1685,7 +1685,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12209,7 +12209,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12271,7 +12271,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_FitGap_BRD-11_BRD_vs_OOTB_vs_Best_Practice_v1.1.xlsx
@@ -12207,7 +12207,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
